--- a/fix/frcoreversion/ig/StructureDefinition-sas-cpts-slot-servicetype-aggregator.xlsx
+++ b/fix/frcoreversion/ig/StructureDefinition-sas-cpts-slot-servicetype-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:59:49+00:00</t>
+    <t>2026-06-16T15:06:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/frcoreversion/ig/StructureDefinition-sas-cpts-slot-servicetype-aggregator.xlsx
+++ b/fix/frcoreversion/ig/StructureDefinition-sas-cpts-slot-servicetype-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T15:06:39+00:00</t>
+    <t>2026-06-17T07:26:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
